--- a/Filtered_V3.0/COCUH_HCA_Florida_Woodmont_Hospital.xlsx
+++ b/Filtered_V3.0/COCUH_HCA_Florida_Woodmont_Hospital.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Abstracting </t>
+          <t>3M (360 Encompass)-ABSDPI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Admissions </t>
+          <t>3M (360 Encompass)-ADMO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Charges </t>
+          <t>3M (360 Encompass)-ITSDIRO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS DI Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-LABRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Lab Results (Discrete) </t>
+          <t>3M (360 Encompass)-OMORDO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-OM Orders </t>
+          <t>3M (360 Encompass)-Patient Accounting</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1237,22 +1237,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople ED Patient Visit Data</t>
+          <t>3M (360 Encompass)-iPeople EDM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Medication Administration</t>
+          <t>3M (360 Encompass)-iPeople Meds</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Nursing Assessment Forms</t>
+          <t>3M (360 Encompass)-iPeople PCS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-Admissions </t>
+          <t>AQuity Solutions (DocEP)-ADMO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-ITS HM Results </t>
+          <t>AQuity Solutions (DocEP)-ITSHMRO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alere (MAS RALS-Plus)-</t>
+          <t>Alere (MAS RALS-Plus)-ADMO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1853,7 +1853,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -1875,7 +1890,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alere (MAS RALS-Plus)-Admissions </t>
+          <t>Alere (MAS RALS-Plus)-labpoc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1920,22 +1935,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Admissions </t>
+          <t>BD (Pyxis Medstation ES)-ADMO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Inventory </t>
+          <t>BD (Pyxis Medstation ES)-PHAINV</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Orders </t>
+          <t>BD (Pyxis Medstation ES)-PHAORD</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Candescent Health/Envision Healthcare (Candescent Health)-</t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-ITSDIRO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2372,7 +2372,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -2394,7 +2409,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candescent Health/Envision Healthcare (Candescent Health)-ITS DI Results </t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-ITSDIRO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2439,7 +2454,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2476,7 +2491,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Candescent Health/Envision Healthcare (Candescent Health)-ITS DI Results </t>
+          <t>Candescent Health/Envision Healthcare (Candescent Health)-radord</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2522,21 +2537,6 @@
       <c r="P27" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-Admissions </t>
+          <t>Computrition (Computrition)-ADMO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-OM Orders </t>
+          <t>Computrition (Computrition)-OMORDO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion Voice)-Admissions </t>
+          <t>Dolbey (Fusion Voice)-ADMO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dolbey (Fusion)-</t>
+          <t>Dolbey (Fusion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3164,7 +3164,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3186,7 +3201,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion)-ITS DI Results </t>
+          <t>Dolbey (Fusion)-radord</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3231,22 +3246,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Admissions </t>
+          <t>Envision Healthcare (Envision Healthcare)-ADMO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS DI Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-CWSO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSDIRO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Scheduling </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3703,22 +3703,22 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Envision Healthcare (Envision Healthcare)-iPeople ED Patient Visit Data</t>
+          <t>Envision Healthcare (Envision Healthcare)-iPeople EDM</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florida HIE (Event Notification Service)-Admissions </t>
+          <t>Florida HIE (Event Notification Service)-ADMO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Admissions </t>
+          <t>GE (CMI - Carescape Gateway)-ADMO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Scheduling </t>
+          <t>GE (CMI - Carescape Gateway)-CWSO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>GE (Centricity - CCG PACS)-</t>
+          <t>GE (Centricity - CCG PACS)-ADMO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4300,6 +4300,21 @@
       <c r="P51" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -4321,7 +4336,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Admissions </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIRO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4371,17 +4386,17 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -4403,7 +4418,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-ITS DI Results </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4448,22 +4463,22 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSDIUI</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Radiology Image Status </t>
         </is>
       </c>
     </row>
@@ -4485,7 +4500,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4567,7 +4582,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-radord</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4612,22 +4627,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>ITSDIUI</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Radiology Image Status </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-</t>
+          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Admissions </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ADMO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-OM Orders </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-OMORDO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Admissions </t>
+          <t>GE (Centricity MUSE)-ADMO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Charges </t>
+          <t>GE (Centricity MUSE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-ITS HM Results </t>
+          <t>GE (Centricity MUSE)-OMORDO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5645,22 +5645,22 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-OM Orders </t>
+          <t>GE (Centricity MUSE)-Patient Accounting</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5727,22 +5727,22 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>GE (Centricity MacLab-DMS/CVPACS to MPF-Patient Folder/HPF Facility)-</t>
+          <t>GE (Centricity MacLab-DMS/CVPACS to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-</t>
+          <t>Google (Healthcare Data Engine - HDE)-ADMO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6145,6 +6145,21 @@
       <c r="P76" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -6166,7 +6181,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Admissions </t>
+          <t>Google (Healthcare Data Engine - HDE)-CWSO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6216,17 +6231,17 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6263,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS DI Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-IMMUN</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6298,17 +6313,17 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6345,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS HM Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSDIRO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6380,7 +6395,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -6390,7 +6405,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -6412,7 +6427,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Lab Results (Discrete) </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6462,7 +6477,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -6472,7 +6487,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -6494,7 +6509,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-MU-Immunizations</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6544,17 +6559,17 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -6576,7 +6591,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-Pathology Results</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES2</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6658,7 +6673,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Pharmacy Orders </t>
+          <t>Google (Healthcare Data Engine - HDE)-PHAORD</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6740,7 +6755,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Scheduling </t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople EDM</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6790,17 +6805,17 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6837,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople ED Patient Visit Data</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople Meds</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6872,17 +6887,17 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6919,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Medication Administration</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople PCS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6954,17 +6969,17 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -6986,7 +7001,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Nursing Assessment Forms</t>
+          <t>Google (Healthcare Data Engine - HDE)-radord</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7032,21 +7047,6 @@
       <c r="P87" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-ADMO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7176,6 +7176,21 @@
       <c r="P89" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -7197,7 +7212,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7243,6 +7258,21 @@
       <c r="P90" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>CWSO</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>iPeople Scheduling</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7294,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7310,6 +7340,21 @@
       <c r="P91" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>CWSO</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>SIU</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -7331,7 +7376,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-IMMUN</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7377,6 +7422,21 @@
       <c r="P92" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>IMMUN</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>VXU</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7458,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Admissions </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7448,17 +7508,17 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -7480,7 +7540,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7562,7 +7622,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-ITSHMRO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7612,7 +7672,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -7622,7 +7682,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -7644,7 +7704,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS HM Results </t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7694,7 +7754,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -7704,7 +7764,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -7726,7 +7786,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7808,7 +7868,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7858,7 +7918,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -7868,7 +7928,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7950,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-MU-Immunizations</t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7940,17 +8000,17 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -7972,7 +8032,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-OM Orders </t>
+          <t>HCA (Cloudera Kafka)-OMORDO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8054,7 +8114,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-PHAORD</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8104,17 +8164,17 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -8136,7 +8196,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-eps</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8182,21 +8242,6 @@
       <c r="P102" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>LABRES2</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8263,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Pharmacy Orders </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8268,17 +8313,17 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8345,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8350,17 +8395,17 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8427,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople Meds</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8432,17 +8477,17 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8509,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8514,17 +8559,17 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8591,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8596,17 +8641,17 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8673,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Medication Administration</t>
+          <t>HCA (Cloudera Kafka)-mr</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8674,21 +8719,6 @@
       <c r="P108" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>iPeople Meds</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr">
-        <is>
-          <t>RAS - iPeople</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8740,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8756,21 +8786,6 @@
       <c r="P109" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8792,7 +8807,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8838,21 +8853,6 @@
       <c r="P110" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (EDW CDM)-Scheduling </t>
+          <t>HCA (EDW CDM)-CWSO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Revive)-ITS HM Results </t>
+          <t>HCA (Revive)-ITSHMRO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>HCA (SMART to Optiflex)-</t>
+          <t>HCA (SMART to Optiflex)-multi</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-ADMO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9398,7 +9398,22 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9420,7 +9435,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9487,7 +9502,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (SMART)-Admissions </t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9532,22 +9547,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Care Management-Facility)-Admissions </t>
+          <t>HCA D&amp;IS (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform to UDS PROi)-ITS HM Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform to UDS PROi)-ITSHMRO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ADMO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9965,6 +9965,21 @@
       <c r="P126" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9986,7 +10001,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Admissions </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -10036,17 +10051,17 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -10068,7 +10083,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS DI Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-IMMUN</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -10118,17 +10133,17 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10165,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS HM Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSDIRO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -10200,7 +10215,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -10210,7 +10225,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -10232,7 +10247,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSHMRO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10282,7 +10297,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -10292,7 +10307,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -10314,7 +10329,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Electronic Lab Reporting</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10364,7 +10379,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>PHELR</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -10374,7 +10389,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>MU-Electronic Lab Reporting</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -10396,7 +10411,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES2</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10446,17 +10461,17 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10493,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10528,17 +10543,17 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -10560,7 +10575,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHAORD</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10610,17 +10625,17 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -10642,7 +10657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-Pathology Results</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHELR</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10692,7 +10707,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHELR</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -10702,7 +10717,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>MU-Electronic Lab Reporting</t>
         </is>
       </c>
     </row>
@@ -10724,7 +10739,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHSS</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10774,17 +10789,17 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10821,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-radord</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10852,21 +10867,6 @@
       <c r="P137" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>CWSO</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr">
-        <is>
-          <t>SIU</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-</t>
+          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Null-Terminates Message)-</t>
+          <t>HCA D&amp;IS (Null-Terminates Message)-iti08</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark to UDS PROi)-</t>
+          <t>HCA D&amp;IS (Waterpark to UDS PROi)-irfpai</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-</t>
+          <t>HCA D&amp;IS (Waterpark)-ADMO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11609,6 +11609,21 @@
       <c r="P148" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -11630,7 +11645,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Admissions </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11680,17 +11695,17 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11727,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS DI Results </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11762,17 +11777,17 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -11794,7 +11809,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS HM Results </t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUN</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11844,17 +11859,17 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11891,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Immunization Query</t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUNQRY</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11958,7 +11973,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (Waterpark)-ITSDIRO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -12008,7 +12023,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -12018,7 +12033,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -12040,7 +12055,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (Waterpark)-ITSHMRO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -12090,17 +12105,17 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -12122,7 +12137,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -12172,17 +12187,17 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -12204,7 +12219,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES2</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -12254,17 +12269,17 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -12286,7 +12301,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12341,12 +12356,12 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -12368,7 +12383,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Pathology Results</t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12418,17 +12433,17 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -12450,7 +12465,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-PHAORD</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -12532,7 +12547,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-PHSS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12582,17 +12597,17 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -12614,7 +12629,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople EDM</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12664,17 +12679,17 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -12696,7 +12711,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople Meds</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12746,17 +12761,17 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -12778,7 +12793,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople PCS</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12828,17 +12843,17 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -12860,7 +12875,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (Waterpark)-radord</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12906,21 +12921,6 @@
       <c r="P164" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (Charge Master)-SMART Procedure Codes </t>
+          <t>HCA Parallon (Charge Master)-MISPROC</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (eCapture)-Admissions </t>
+          <t>HCA Parallon (eCapture)-ADMO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Admissions </t>
+          <t>Health Catalyst (HCare Hub)-ADMO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS DI Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSDIRO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS HM Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSHMRO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Lab Results (Discrete) </t>
+          <t>Health Catalyst (HCare Hub)-LABRES</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Health Catalyst (HCare Hub)-Pathology Results</t>
+          <t>Health Catalyst (HCare Hub)-LABRES2</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Admissions </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-ADMO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Clinical Monitoring Results </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-PCSCMI</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Admissions </t>
+          <t>Hospira (Theradoc)-ADMO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS DI Results </t>
+          <t>Hospira (Theradoc)-ITSDIRO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS HM Results </t>
+          <t>Hospira (Theradoc)-ITSHMRO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -14236,7 +14236,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Lab Results (Discrete) </t>
+          <t>Hospira (Theradoc)-LABRES</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-OM Orders </t>
+          <t>Hospira (Theradoc)-OMORDO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Pharmacy Orders </t>
+          <t>Hospira (Theradoc)-PHAORD</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople ED Patient Visit Data</t>
+          <t>Hospira (Theradoc)-iPeople EDM</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Medication Administration</t>
+          <t>Hospira (Theradoc)-iPeople Meds</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Nursing Assessment Forms</t>
+          <t>Hospira (Theradoc)-iPeople PCS</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase RX-ADT/Link Orders)-Admissions </t>
+          <t>Hyland (Onbase RX-ADT/Link Orders)-ADMO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase)-Admissions </t>
+          <t>Hyland (Onbase)-ADMO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -15207,7 +15207,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Consent Management)-Admissions </t>
+          <t>IBM (Consent Management)-ADMO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">IM Practice Manager (Ingenious Med)-Admissions </t>
+          <t>IM Practice Manager (Ingenious Med)-ADMO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Admissions </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-ADMO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Tissue Tracking </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-SURTSD</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-</t>
+          <t>Iodine Software (Iodine-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -15993,6 +15993,21 @@
       <c r="P205" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -16014,7 +16029,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Admissions </t>
+          <t>Iodine Software (Iodine-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -16064,17 +16079,17 @@
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -16096,7 +16111,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS DI Results </t>
+          <t>Iodine Software (Iodine-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -16146,7 +16161,7 @@
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
@@ -16156,7 +16171,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -16178,7 +16193,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS HM Results </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -16228,7 +16243,7 @@
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
@@ -16238,7 +16253,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -16260,7 +16275,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Lab Results (Discrete) </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES2</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -16310,7 +16325,7 @@
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
@@ -16320,7 +16335,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -16342,7 +16357,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-OM Orders </t>
+          <t>Iodine Software (Iodine-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -16424,7 +16439,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-Pathology Results</t>
+          <t>Iodine Software (Iodine-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -16474,17 +16489,17 @@
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -16506,7 +16521,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Pharmacy Orders </t>
+          <t>Iodine Software (Iodine-Facility)-iPeople EDM</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -16556,17 +16571,17 @@
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -16588,7 +16603,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople ED Patient Visit Data</t>
+          <t>Iodine Software (Iodine-Facility)-iPeople Meds</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -16638,17 +16653,17 @@
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -16670,7 +16685,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople Medication Administration</t>
+          <t>Iodine Software (Iodine-Facility)-iPeople PCS</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -16720,17 +16735,17 @@
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -16752,7 +16767,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-iPeople Nursing Assessment Forms</t>
+          <t>Iodine Software (Iodine-Facility)-radord</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -16798,21 +16813,6 @@
       <c r="P215" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q215" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R215" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -16896,7 +16896,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">MSN Healthcare Solutions (Intellirad)-Admissions </t>
+          <t>MSN Healthcare Solutions (Intellirad)-ADMO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">MSN Healthcare Solutions (Intellirad)-ITS DI Results </t>
+          <t>MSN Healthcare Solutions (Intellirad)-ITSDIRO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKesson (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>McKesson (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Admissions </t>
+          <t>Medaxion (Medaxion Pulse)-ADMO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Scheduling </t>
+          <t>Medaxion (Medaxion Pulse)-CWSO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">MediMobile (MediMobile)-Admissions </t>
+          <t>MediMobile (MediMobile)-ADMO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -17780,7 +17780,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-</t>
+          <t>Meditech (HCA 5.6)-ADMO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -17826,6 +17826,21 @@
       <c r="P229" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -17847,7 +17862,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Admissions </t>
+          <t>Meditech (HCA 5.6)-ITSDIRO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -17897,17 +17912,17 @@
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -17929,7 +17944,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS DI Results </t>
+          <t>Meditech (HCA 5.6)-ITSHMRO</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -17979,7 +17994,7 @@
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
@@ -17989,7 +18004,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -18011,7 +18026,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS HM Results </t>
+          <t>Meditech (HCA 5.6)-LABRES</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -18061,7 +18076,7 @@
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
@@ -18071,7 +18086,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -18093,7 +18108,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Lab Results (Discrete) </t>
+          <t>Meditech (HCA 5.6)-LABRES2</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -18143,7 +18158,7 @@
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
@@ -18153,7 +18168,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18190,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-OM Orders </t>
+          <t>Meditech (HCA 5.6)-OMORDO</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -18257,7 +18272,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-Pathology Results</t>
+          <t>Meditech (HCA 5.6)-PHAORD</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -18307,17 +18322,17 @@
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -18339,7 +18354,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Pharmacy Orders </t>
+          <t>Meditech (HCA 5.6)-radord</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -18385,21 +18400,6 @@
       <c r="P236" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q236" t="inlineStr">
-        <is>
-          <t>PHAORD</t>
-        </is>
-      </c>
-      <c r="R236" t="inlineStr">
-        <is>
-          <t>RDE</t>
-        </is>
-      </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Admissions </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ADMO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -18647,7 +18647,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -18729,7 +18729,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -18955,7 +18955,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mednax (BabySteps Cloud)-Admissions </t>
+          <t>Mednax (BabySteps Cloud)-ADMO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mednax (BabySteps Cloud)-ITS HM Results </t>
+          <t>Mednax (BabySteps Cloud)-ITSHMRO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -19181,7 +19181,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -19345,7 +19345,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS DI Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -19427,7 +19427,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -19653,7 +19653,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Admissions </t>
+          <t>Mobile Heartbeat (imobile)-ADMO</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -19735,7 +19735,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Lab Results (Discrete) </t>
+          <t>Mobile Heartbeat (imobile)-LABRES</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -19879,7 +19879,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (Wound Care)-Admissions </t>
+          <t>Net Health (Wound Care)-ADMO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -19961,7 +19961,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (Wound Care)-Charges </t>
+          <t>Net Health (Wound Care)-Patient Accounting</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Netsmart (UDS PROi to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>Netsmart (UDS PROi to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Netsmart (UDS PROi to PA)-Case Mix Group</t>
+          <t>Netsmart (UDS PROi to PA)-nan</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -20388,7 +20388,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Netsmart (UDS PROi)-Admissions </t>
+          <t>Netsmart (UDS PROi)-ADMO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Netsmart (UDS PROi)-Admissions </t>
+          <t>Netsmart (UDS PROi)-ADMO</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Omnicell (Optiflex to SMART)-</t>
+          <t>Omnicell (Optiflex to SMART)-mmrepl</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -20743,7 +20743,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Admissions </t>
+          <t>Omnicell (Optiflex)-ADMO</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -20825,7 +20825,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Charges </t>
+          <t>Omnicell (Optiflex)-Patient Accounting</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -20969,7 +20969,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport Health Communications, Inc. (eCare Next)-Admissions </t>
+          <t>Passport Health Communications, Inc. (eCare Next)-ADMO</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Patient Keeper (Portal)-</t>
+          <t>Patient Keeper (Portal)-ITSHMRO</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -21159,6 +21159,21 @@
       <c r="P273" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>ITSHMRO</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -21180,7 +21195,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient Keeper (Portal)-ITS HM Results </t>
+          <t>Patient Keeper (Portal)-eps</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -21226,21 +21241,6 @@
       <c r="P274" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q274" t="inlineStr">
-        <is>
-          <t>ITSHMRO</t>
-        </is>
-      </c>
-      <c r="R274" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -21324,7 +21324,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Provation (Apex to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Provation (Apex to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-Admissions </t>
+          <t>Provation (Apex)-ADMO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -21535,7 +21535,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-ITS HM Results </t>
+          <t>Provation (Apex)-CWSO</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -21580,22 +21580,22 @@
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-Scheduling </t>
+          <t>Provation (Apex)-ITSHMRO</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -21662,22 +21662,22 @@
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Provation (MD - CMORE to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Provation (MD - CMORE to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rauland (Responder)-Admissions </t>
+          <t>Rauland (Responder)-ADMO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Team Health (Team Health)-Admissions </t>
+          <t>Team Health (Team Health)-ADMO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -22178,7 +22178,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-Admissions </t>
+          <t>TeleSpecialists (TeleCare)-ADMO</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-ITS HM Results </t>
+          <t>TeleSpecialists (TeleCare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-OM Orders </t>
+          <t>TeleSpecialists (TeleCare)-OMORDO</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -22486,7 +22486,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-Admissions </t>
+          <t>TeleTracking (TransferCenter IQ)-ADMO</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-OM Orders </t>
+          <t>TeleTracking (TransferCenter IQ)-OMORDO</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -22650,7 +22650,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>TeleTracking (TransferCenter IQ)-iPeople Nursing Assessment Forms</t>
+          <t>TeleTracking (TransferCenter IQ)-iPeople PCS</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Ventana Medical Systems (VANTAGE)-</t>
+          <t>Ventana Medical Systems (VANTAGE)-pthord</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -22923,7 +22923,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Admissions </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -23005,7 +23005,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITS DI Results </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Lab Results (Discrete) </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -23169,7 +23169,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -23333,7 +23333,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Pharmacy Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -23415,7 +23415,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople ED Patient Visit Data</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople EDM</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -23497,7 +23497,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Medication Administration</t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-iPeople Meds</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -23641,7 +23641,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-</t>
+          <t>dbMotion (db Motion)-ADMO</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -23687,6 +23687,21 @@
       <c r="P307" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -23708,7 +23723,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-</t>
+          <t>dbMotion (db Motion)-IMMUN</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -23754,6 +23769,21 @@
       <c r="P308" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>IMMUN</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>VXU</t>
+        </is>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -23775,7 +23805,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-</t>
+          <t>dbMotion (db Motion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -23821,6 +23851,21 @@
       <c r="P309" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -23842,7 +23887,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Admissions </t>
+          <t>dbMotion (db Motion)-ITSHMRO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -23892,17 +23937,17 @@
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -23924,7 +23969,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS DI Results </t>
+          <t>dbMotion (db Motion)-LABRES</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -23974,7 +24019,7 @@
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -23984,7 +24029,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -24006,7 +24051,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS HM Results </t>
+          <t>dbMotion (db Motion)-LABRES2</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -24056,7 +24101,7 @@
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -24066,7 +24111,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -24088,7 +24133,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Lab Results (Discrete) </t>
+          <t>dbMotion (db Motion)-PHAORD</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -24138,17 +24183,17 @@
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -24170,7 +24215,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-MU-Immunizations</t>
+          <t>dbMotion (db Motion)-eps</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -24216,21 +24261,6 @@
       <c r="P314" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q314" t="inlineStr">
-        <is>
-          <t>IMMUN</t>
-        </is>
-      </c>
-      <c r="R314" t="inlineStr">
-        <is>
-          <t>VXU</t>
-        </is>
-      </c>
-      <c r="S314" t="inlineStr">
-        <is>
-          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -24252,7 +24282,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-Pathology Results</t>
+          <t>dbMotion (db Motion)-iPeople EDM</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -24302,17 +24332,17 @@
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -24334,7 +24364,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Pharmacy Orders </t>
+          <t>dbMotion (db Motion)-iPeople PCS</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -24384,17 +24414,17 @@
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -24416,7 +24446,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople ED Patient Visit Data</t>
+          <t>dbMotion (db Motion)-mr</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -24462,21 +24492,6 @@
       <c r="P317" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q317" t="inlineStr">
-        <is>
-          <t>iPeople EDM</t>
-        </is>
-      </c>
-      <c r="R317" t="inlineStr">
-        <is>
-          <t>EDM - iPeople</t>
-        </is>
-      </c>
-      <c r="S317" t="inlineStr">
-        <is>
-          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -24498,7 +24513,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople Nursing Assessment Forms</t>
+          <t>dbMotion (db Motion)-radord</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -24544,21 +24559,6 @@
       <c r="P318" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q318" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R318" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S318" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -24642,7 +24642,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (HCA 5.6)-iPeople EDM</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople Medication Administration</t>
+          <t>iPeople (HCA 5.6)-iPeople Meds</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -24868,7 +24868,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">iPeople (iPeople MT56)-OM Orders </t>
+          <t>iPeople (iPeople MT56)-OMORDO</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -24950,7 +24950,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (iPeople MT56)-iPeople EDM</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -25032,7 +25032,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Medication Administration</t>
+          <t>iPeople (iPeople MT56)-iPeople Meds</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -25114,7 +25114,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Nursing Assessment Forms</t>
+          <t>iPeople (iPeople MT56)-iPeople PCS</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
